--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="173">
   <si>
     <t>_reportFile</t>
   </si>
@@ -49,13 +49,487 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-04-01T18:39:19.586Z</t>
+    <t>2026-04-04T20:18:03.055Z</t>
   </si>
   <si>
     <t>Intel Inside - Built for AI</t>
   </si>
   <si>
     <t>https://www.intel.com/content/www/us/en/homepage.html</t>
+  </si>
+  <si>
+    <t>support.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news","cards-news"]</t>
+  </si>
+  <si>
+    <t>support</t>
+  </si>
+  <si>
+    <t>institutional-landing</t>
+  </si>
+  <si>
+    <t>2026-04-04T20:12:21.769Z</t>
+  </si>
+  <si>
+    <t>Intel Support</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/support.html</t>
+  </si>
+  <si>
+    <t>ai-pc/overview.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product","cards-product","cards-product","cards-product","cards-product","cards-product","columns","columns","columns","cards-resource"]</t>
+  </si>
+  <si>
+    <t>ai-pc/overview</t>
+  </si>
+  <si>
+    <t>marketing-landing</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:16.627Z</t>
+  </si>
+  <si>
+    <t>The AI PC Powered by Intel. Now AI Is for Everyone</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/ai-pc/overview.html</t>
+  </si>
+  <si>
+    <t>artificial-intelligence/analytics.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards-product","cards-product","cards-product","cards-resource"]</t>
+  </si>
+  <si>
+    <t>artificial-intelligence/analytics</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:48.245Z</t>
+  </si>
+  <si>
+    <t>Advanced Analytics Solutions – Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/artificial-intelligence/analytics.html</t>
+  </si>
+  <si>
+    <t>artificial-intelligence/overview.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product","cards-product","cards-product","cards-resource"]</t>
+  </si>
+  <si>
+    <t>artificial-intelligence/overview</t>
+  </si>
+  <si>
+    <t>2026-04-04T20:12:07.568Z</t>
+  </si>
+  <si>
+    <t>Explore Intel® Artificial Intelligence Solutions</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/artificial-intelligence/overview.html</t>
+  </si>
+  <si>
+    <t>artificial-intelligence/processors.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product","cards-product","cards-product","cards-product","columns","columns","columns"]</t>
+  </si>
+  <si>
+    <t>artificial-intelligence/processors</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:23.438Z</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence (AI) Processors – Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/artificial-intelligence/processors.html</t>
+  </si>
+  <si>
+    <t>artificial-intelligence/responsible-ai.report.json</t>
+  </si>
+  <si>
+    <t>artificial-intelligence/responsible-ai</t>
+  </si>
+  <si>
+    <t>2026-04-03T21:01:14.288Z</t>
+  </si>
+  <si>
+    <t>Responsible AI</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/artificial-intelligence/responsible-ai.html</t>
+  </si>
+  <si>
+    <t>cloud-computing/overview.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>cloud-computing/overview</t>
+  </si>
+  <si>
+    <t>category-directory</t>
+  </si>
+  <si>
+    <t>2026-04-03T21:00:06.719Z</t>
+  </si>
+  <si>
+    <t>Cloud Computing Solutions – Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/cloud-computing/overview.html</t>
+  </si>
+  <si>
+    <t>company-overview/company-overview.report.json</t>
+  </si>
+  <si>
+    <t>company-overview/company-overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T21:01:07.254Z</t>
+  </si>
+  <si>
+    <t>Innovation starts here</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/company-overview/company-overview.html</t>
+  </si>
+  <si>
+    <t>corporate-responsibility/corporate-responsibility.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news","cards-news","cards-news","cards-news","cards-news","cards-news","cards-news","cards-news","cards-news"]</t>
+  </si>
+  <si>
+    <t>corporate-responsibility/corporate-responsibility</t>
+  </si>
+  <si>
+    <t>2026-04-04T20:12:26.817Z</t>
+  </si>
+  <si>
+    <t>Corporate Social Responsibility</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/corporate-responsibility/corporate-responsibility.html</t>
+  </si>
+  <si>
+    <t>data-center/overview.report.json</t>
+  </si>
+  <si>
+    <t>data-center/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T21:00:13.072Z</t>
+  </si>
+  <si>
+    <t>Data Center Solutions – Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/data-center/overview.html</t>
+  </si>
+  <si>
+    <t>developer/overview.report.json</t>
+  </si>
+  <si>
+    <t>developer/overview</t>
+  </si>
+  <si>
+    <t>2026-04-04T20:12:17.506Z</t>
+  </si>
+  <si>
+    <t>Intel Developer Zone</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/developer/overview.html</t>
+  </si>
+  <si>
+    <t>edge-computing/overview.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product","cards-product","cards-product","columns","columns","retailer-locator","retailer-locator","retailer-locator","retailer-locator","cards-resource"]</t>
+  </si>
+  <si>
+    <t>edge-computing/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:36.863Z</t>
+  </si>
+  <si>
+    <t>Edge Computing Solutions – Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/edge-computing/overview.html</t>
+  </si>
+  <si>
+    <t>environment/sustainability.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards-product","cards-product","cards-product","cards-product","retailer-locator"]</t>
+  </si>
+  <si>
+    <t>environment/sustainability</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:58.658Z</t>
+  </si>
+  <si>
+    <t>Sustainable Computing for a Sustainable Future</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/environment/sustainability.html</t>
+  </si>
+  <si>
+    <t>gaming/esports.report.json</t>
+  </si>
+  <si>
+    <t>["hero"]</t>
+  </si>
+  <si>
+    <t>gaming/esports</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:09.629Z</t>
+  </si>
+  <si>
+    <t>Esports: Transforming the Future of Gaming Technology - Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/gaming/esports.html</t>
+  </si>
+  <si>
+    <t>gaming/gaming-desktops.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards-product","cards-product","cards-product","cards-product","cards-product","columns","columns","columns","columns","retailer-locator","retailer-locator","cards-resource"]</t>
+  </si>
+  <si>
+    <t>gaming/gaming-desktops</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:57:56.946Z</t>
+  </si>
+  <si>
+    <t>Gaming Desktops Powered by Intel Core Ultra 200S Plus</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/gaming/gaming-desktops.html</t>
+  </si>
+  <si>
+    <t>gaming/gaming-laptops.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards-resource"]</t>
+  </si>
+  <si>
+    <t>gaming/gaming-laptops</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:02.540Z</t>
+  </si>
+  <si>
+    <t>Gaming Laptops Powered by Intel® Core Ultra Series 2</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/gaming/gaming-laptops.html</t>
+  </si>
+  <si>
+    <t>gaming/serious-gaming.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards-product","cards-product","cards-product","cards-product","cards-product","cards-product","cards-product","columns","columns","columns","columns","columns","columns","retailer-locator","cards-resource"]</t>
+  </si>
+  <si>
+    <t>gaming/serious-gaming</t>
+  </si>
+  <si>
+    <t>2026-04-04T20:12:01.631Z</t>
+  </si>
+  <si>
+    <t>Next‑Gen Gaming PCs Powered by Intel® Core™ Ultra Series 2</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/gaming/serious-gaming.html</t>
+  </si>
+  <si>
+    <t>high-performance-computing/overview.report.json</t>
+  </si>
+  <si>
+    <t>high-performance-computing/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T21:00:23.027Z</t>
+  </si>
+  <si>
+    <t>High Performance Computing (HPC) Solutions - Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/high-performance-computing/overview.html</t>
+  </si>
+  <si>
+    <t>manufacturing/manufacturing-industrial-overview.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product","cards-product","cards-product","cards-product","cards-product","cards-product","columns","columns"]</t>
+  </si>
+  <si>
+    <t>manufacturing/manufacturing-industrial-overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:53.206Z</t>
+  </si>
+  <si>
+    <t>Industry 4.0 and Smart Manufacturing Technology Solutions Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/manufacturing/manufacturing-industrial-overview.html</t>
+  </si>
+  <si>
+    <t>products/overview.report.json</t>
+  </si>
+  <si>
+    <t>products/overview</t>
+  </si>
+  <si>
+    <t>2026-04-04T20:12:11.668Z</t>
+  </si>
+  <si>
+    <t>Intel® Core™ Processors, FPGAs, GPUs, Networking, Software</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/products/overview.html</t>
+  </si>
+  <si>
+    <t>security/overview.report.json</t>
+  </si>
+  <si>
+    <t>security/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T21:00:17.973Z</t>
+  </si>
+  <si>
+    <t>Security Innovation for Business Networks | Intel®</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/security/overview.html</t>
+  </si>
+  <si>
+    <t>topics/overview.report.json</t>
+  </si>
+  <si>
+    <t>topics/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T21:00:01.146Z</t>
+  </si>
+  <si>
+    <t>Topics</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/topics/overview.html</t>
+  </si>
+  <si>
+    <t>developer/programs/overview.report.json</t>
+  </si>
+  <si>
+    <t>developer/programs/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:59:56.695Z</t>
+  </si>
+  <si>
+    <t>Developer Programs from Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/developer/programs/overview.html</t>
+  </si>
+  <si>
+    <t>developer/tools/overview.report.json</t>
+  </si>
+  <si>
+    <t>developer/tools/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:59:51.171Z</t>
+  </si>
+  <si>
+    <t>Development Tools</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/developer/tools/overview.html</t>
+  </si>
+  <si>
+    <t>developer/topic-technology/overview.report.json</t>
+  </si>
+  <si>
+    <t>developer/topic-technology/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:59:46.073Z</t>
+  </si>
+  <si>
+    <t>Development Technologies</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/developer/topic-technology/overview.html</t>
+  </si>
+  <si>
+    <t>gaming/resources/overview.report.json</t>
+  </si>
+  <si>
+    <t>gaming/resources/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:59:41.422Z</t>
+  </si>
+  <si>
+    <t>Intel® Gaming-Technik und -Produkte – Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/gaming/resources/overview.html</t>
+  </si>
+  <si>
+    <t>products/details/processors/core-ultra.report.json</t>
+  </si>
+  <si>
+    <t>products/details/processors/core-ultra</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:29.188Z</t>
+  </si>
+  <si>
+    <t>New Intel® Core™ Ultra Series 3 Processors</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/products/details/processors/core-ultra.html</t>
+  </si>
+  <si>
+    <t>products/docs/discrete-gpus/arc/desktop/b-series/overview.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product","columns","columns","columns","columns","cards-resource"]</t>
+  </si>
+  <si>
+    <t>products/docs/discrete-gpus/arc/desktop/b-series/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:42.572Z</t>
+  </si>
+  <si>
+    <t>Intel® Arc™ B-Series Graphics for Desktops</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/products/docs/discrete-gpus/arc/desktop/b-series/overview.html</t>
   </si>
 </sst>
 </file>
@@ -444,16 +918,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="29" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -506,6 +977,734 @@
       </c>
       <c r="H2" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="s">
+        <v>107</v>
+      </c>
+      <c r="G18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H18" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" t="s">
+        <v>113</v>
+      </c>
+      <c r="G19" t="s">
+        <v>114</v>
+      </c>
+      <c r="H19" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G21" t="s">
+        <v>125</v>
+      </c>
+      <c r="H21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22" t="s">
+        <v>130</v>
+      </c>
+      <c r="H22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" t="s">
+        <v>133</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" t="s">
+        <v>134</v>
+      </c>
+      <c r="G23" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" t="s">
+        <v>139</v>
+      </c>
+      <c r="G24" t="s">
+        <v>140</v>
+      </c>
+      <c r="H24" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" t="s">
+        <v>144</v>
+      </c>
+      <c r="G25" t="s">
+        <v>145</v>
+      </c>
+      <c r="H25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>148</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" t="s">
+        <v>149</v>
+      </c>
+      <c r="G26" t="s">
+        <v>150</v>
+      </c>
+      <c r="H26" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>152</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" t="s">
+        <v>154</v>
+      </c>
+      <c r="G27" t="s">
+        <v>155</v>
+      </c>
+      <c r="H27" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" t="s">
+        <v>158</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" t="s">
+        <v>159</v>
+      </c>
+      <c r="G28" t="s">
+        <v>160</v>
+      </c>
+      <c r="H28" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>162</v>
+      </c>
+      <c r="B29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" t="s">
+        <v>163</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" t="s">
+        <v>164</v>
+      </c>
+      <c r="G29" t="s">
+        <v>165</v>
+      </c>
+      <c r="H29" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>167</v>
+      </c>
+      <c r="B30" t="s">
+        <v>168</v>
+      </c>
+      <c r="C30" t="s">
+        <v>169</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" t="s">
+        <v>170</v>
+      </c>
+      <c r="G30" t="s">
+        <v>171</v>
+      </c>
+      <c r="H30" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
